--- a/resources/templates/standard/J1100-02.xlsx
+++ b/resources/templates/standard/J1100-02.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve"> 공 정 흐 름 도</t>
   </si>
@@ -754,11 +757,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -796,7 +801,7 @@
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -804,7 +809,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="5"/>
@@ -813,7 +818,7 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -821,7 +826,7 @@
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="8"/>
@@ -830,7 +835,7 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -838,7 +843,7 @@
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="10"/>
@@ -847,60 +852,60 @@
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7" s="13"/>
       <c r="J7" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="11"/>
       <c r="K8" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
